--- a/data/satisfaction_detail/2026/1-6月/自助餐.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/自助餐.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.56</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>9.890000000000001</v>
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.84</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>10</v>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.4</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10</v>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="8">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.9</v>
+        <v>9.81</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>10</v>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>9.27</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>9.779999999999999</v>
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.6</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>10</v>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9.550000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>10</v>

--- a/data/satisfaction_detail/2026/1-6月/自助餐.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/自助餐.xlsx
@@ -520,7 +520,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>菜品口味口相</t>
+          <t>菜品口味品相</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
